--- a/자료/작업계획.xlsx
+++ b/자료/작업계획.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\T3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User-42\Desktop\Project\T3\자료\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2013329-8FCC-4171-ABA9-F7A5D1DE6081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BE56B9F-6209-4645-ABC0-5AA54E15CB57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="83">
   <si>
     <t>FSM 기반 유닛 상태</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -300,6 +300,62 @@
   </si>
   <si>
     <t>버튼 터치시 싱글톤에서 버튼 눌렀는지 안눌렀는지 관리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>멀티플레이 기능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>협력 보스 레이드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아군 타워 있음 깨지면 패배 반대로 보스를 잡으면 승리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>적은 고정된 숫자가 나오면 스폰X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>레디 데이터는 4개의 유닛을 가지고 있음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어1 유닛, 프리뷰 유닛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어2 유닛, 프리뷰 유닛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일단 이런식으로 가지고 있고 이건 호스트 클라에 따라서 플레이어1, 2를 나눔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>버튼 누르면 일단 소환함 프리뷰 유닛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그 뒤로 다시 눌렀을떄가 확정 배치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그뒤로 3초를 샘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이떄 시계 빙글빙글 돌아가는 UI만들자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보스 HP바 구현해야됨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>프리뷰 유닉 삭제 및 진짜 유닛으로 교체</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -625,7 +681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C5:AG71"/>
+  <dimension ref="C5:AG95"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="5" spans="3:18" x14ac:dyDescent="0.45">
@@ -930,6 +986,72 @@
     <row r="71" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C71" t="s">
         <v>66</v>
+      </c>
+    </row>
+    <row r="76" spans="3:14" x14ac:dyDescent="0.45">
+      <c r="C76" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="78" spans="3:14" x14ac:dyDescent="0.45">
+      <c r="C78" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="79" spans="3:14" x14ac:dyDescent="0.45">
+      <c r="C79" t="s">
+        <v>71</v>
+      </c>
+      <c r="I79" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="81" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C81" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="83" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C83" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="85" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C85" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="86" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C86" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="88" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C88" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="90" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C90" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="91" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C91" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="93" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C93" t="s">
+        <v>79</v>
+      </c>
+      <c r="E93" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="95" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C95" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/자료/작업계획.xlsx
+++ b/자료/작업계획.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User-42\Desktop\Project\T3\자료\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BE56B9F-6209-4645-ABC0-5AA54E15CB57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B44F877B-5AAD-4471-AF2D-43FEB76917C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="15930" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="89">
   <si>
     <t>FSM 기반 유닛 상태</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -357,13 +357,32 @@
   <si>
     <t>프리뷰 유닉 삭제 및 진짜 유닛으로 교체</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>네트워크 유닛 배치 파이프라인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 플레이어가 버튼을 눌러서 로컬 레디객체 소환</t>
+  </si>
+  <si>
+    <t>2. 드래그앤 드롭으로 유닛 배치</t>
+  </si>
+  <si>
+    <t>3. 해당 배치 성공시 네트워크 레디 유닛으로 변경(네트워크 유닛{진짜유닛}도 미리 소환 서버에 로딩하기위해)</t>
+  </si>
+  <si>
+    <t>4. 3초 뒤에 일반 네트워크 유닛을 레디 유닛이 있는곳으로 이동</t>
+  </si>
+  <si>
+    <t>5. 게임 시작</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -377,6 +396,13 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -399,8 +425,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -683,6 +712,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="C5:AG95"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="15" max="15" width="32" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="5" spans="3:18" x14ac:dyDescent="0.45">
       <c r="C5" t="s">
@@ -954,7 +986,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="67" spans="3:14" x14ac:dyDescent="0.45">
+    <row r="67" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C67" t="s">
         <v>62</v>
       </c>
@@ -962,7 +994,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="68" spans="3:14" x14ac:dyDescent="0.45">
+    <row r="68" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C68" t="s">
         <v>63</v>
       </c>
@@ -970,7 +1002,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="3:14" x14ac:dyDescent="0.45">
+    <row r="69" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C69" t="s">
         <v>64</v>
       </c>
@@ -978,32 +1010,56 @@
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="3:14" x14ac:dyDescent="0.45">
+    <row r="70" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C70" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="71" spans="3:14" x14ac:dyDescent="0.45">
+    <row r="71" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C71" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="3:14" x14ac:dyDescent="0.45">
+    <row r="75" spans="3:15" x14ac:dyDescent="0.45">
+      <c r="O75" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="76" spans="3:15" ht="32" x14ac:dyDescent="0.45">
       <c r="C76" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="78" spans="3:14" x14ac:dyDescent="0.45">
+      <c r="O76" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="77" spans="3:15" x14ac:dyDescent="0.45">
+      <c r="O77" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="78" spans="3:15" ht="92.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C78" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="79" spans="3:14" x14ac:dyDescent="0.45">
+      <c r="O78" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="79" spans="3:15" ht="32" x14ac:dyDescent="0.45">
       <c r="C79" t="s">
         <v>71</v>
       </c>
       <c r="I79" t="s">
         <v>81</v>
+      </c>
+      <c r="O79" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="80" spans="3:15" x14ac:dyDescent="0.45">
+      <c r="O80" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="81" spans="3:5" x14ac:dyDescent="0.45">

--- a/자료/작업계획.xlsx
+++ b/자료/작업계획.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User-42\Desktop\Project\T3\자료\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B44F877B-5AAD-4471-AF2D-43FEB76917C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02B85775-4D67-4981-98EE-6D4C0B371632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="15930" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="104">
   <si>
     <t>FSM 기반 유닛 상태</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -376,6 +376,66 @@
   </si>
   <si>
     <t>5. 게임 시작</t>
+  </si>
+  <si>
+    <t>배치 파이프라인 다시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>프리뷰 유닛에 필ㅇㅎ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>배치 파이프라인 ver 네트워크</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 플레이어가 터치 앤 드래그로 유닛 배치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 해당 배치 성공 or 실패 여부 확인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. 성공시 해당 유닛 삭제(로컬 프리뷰 유닛)후 네트워크 레디 유닛으로 변경</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4. 3초 뒤에 네트워크 레디 유닛 삭제 및 실제 네트워크 유닛으로 생성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>프리뷰 유닛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>네트워크 레디 유닛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로컬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>네트워크</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>네트워크 실제 유닛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>호스트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>클라</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2인용 게임이니까</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -710,7 +770,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C5:AG95"/>
+  <dimension ref="C5:AG104"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="15" max="15" width="32" bestFit="1" customWidth="1"/>
@@ -1062,42 +1122,50 @@
         <v>88</v>
       </c>
     </row>
-    <row r="81" spans="3:5" x14ac:dyDescent="0.45">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C81" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="83" spans="3:5" x14ac:dyDescent="0.45">
+    <row r="83" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C83" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="85" spans="3:5" x14ac:dyDescent="0.45">
+    <row r="84" spans="3:15" x14ac:dyDescent="0.45">
+      <c r="O84" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C85" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="86" spans="3:5" x14ac:dyDescent="0.45">
+    <row r="86" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C86" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="88" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="O86" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C88" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="90" spans="3:5" x14ac:dyDescent="0.45">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C90" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="91" spans="3:5" x14ac:dyDescent="0.45">
+    <row r="91" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C91" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="93" spans="3:5" x14ac:dyDescent="0.45">
+    <row r="93" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C93" t="s">
         <v>79</v>
       </c>
@@ -1105,9 +1173,72 @@
         <v>80</v>
       </c>
     </row>
-    <row r="95" spans="3:5" x14ac:dyDescent="0.45">
+    <row r="95" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C95" t="s">
         <v>82</v>
+      </c>
+    </row>
+    <row r="99" spans="4:17" x14ac:dyDescent="0.45">
+      <c r="D99" t="s">
+        <v>91</v>
+      </c>
+      <c r="P99" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="100" spans="4:17" x14ac:dyDescent="0.45">
+      <c r="O100" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="101" spans="4:17" x14ac:dyDescent="0.45">
+      <c r="D101" t="s">
+        <v>92</v>
+      </c>
+      <c r="N101" t="s">
+        <v>98</v>
+      </c>
+      <c r="O101" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="102" spans="4:17" x14ac:dyDescent="0.45">
+      <c r="D102" t="s">
+        <v>93</v>
+      </c>
+      <c r="N102" t="s">
+        <v>99</v>
+      </c>
+      <c r="O102" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="103" spans="4:17" x14ac:dyDescent="0.45">
+      <c r="D103" t="s">
+        <v>94</v>
+      </c>
+      <c r="N103" t="s">
+        <v>99</v>
+      </c>
+      <c r="O103" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="104" spans="4:17" x14ac:dyDescent="0.45">
+      <c r="D104" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/자료/작업계획.xlsx
+++ b/자료/작업계획.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User-42\Desktop\Project\T3\자료\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\psdd2\Desktop\project\T3_Why_Me_unuty\자료\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02B85775-4D67-4981-98EE-6D4C0B371632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19CC636A-DFD3-440D-B28A-52043788F7DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="15930" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="111">
   <si>
     <t>FSM 기반 유닛 상태</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -435,6 +435,34 @@
   </si>
   <si>
     <t>2인용 게임이니까</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>남은 작업</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 적 레디유닛 만들어야됨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. UI 작업</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 적 플레이어 AI (3개를 만들꺼고 각각 이지 노말 하드 버전으로 만들어야됨 하나를 만들고 코스트 충전량에 따라서 난이도를 세분화 할꺼임)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4. 적베이스, 아군베이스 제작(클래시 로얄류 성같은 느낌 클래시 로얄은 3개를 만들었지만 나는 하나만 할꺼임)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5. 전투 승패 파이프라인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6. 이에 따른 매치메이킹 시스템 다듬기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -770,18 +798,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C5:AG104"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <dimension ref="C5:AG119"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="15" max="15" width="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="3:18" x14ac:dyDescent="0.45">
+    <row r="5" spans="3:18" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="3:18" x14ac:dyDescent="0.45">
+    <row r="7" spans="3:18" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
         <v>1</v>
       </c>
@@ -789,7 +817,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="3:18" x14ac:dyDescent="0.45">
+    <row r="8" spans="3:18" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
         <v>3</v>
       </c>
@@ -797,7 +825,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="3:18" x14ac:dyDescent="0.45">
+    <row r="9" spans="3:18" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
         <v>2</v>
       </c>
@@ -805,7 +833,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="3:18" x14ac:dyDescent="0.45">
+    <row r="10" spans="3:18" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
         <v>4</v>
       </c>
@@ -813,12 +841,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="3:18" x14ac:dyDescent="0.45">
+    <row r="11" spans="3:18" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="3:18" x14ac:dyDescent="0.45">
+    <row r="12" spans="3:18" x14ac:dyDescent="0.3">
       <c r="C12" t="s">
         <v>6</v>
       </c>
@@ -826,12 +854,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="3:18" x14ac:dyDescent="0.45">
+    <row r="13" spans="3:18" x14ac:dyDescent="0.3">
       <c r="C13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="3:18" x14ac:dyDescent="0.45">
+    <row r="14" spans="3:18" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
         <v>8</v>
       </c>
@@ -839,12 +867,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="3:18" x14ac:dyDescent="0.45">
+    <row r="15" spans="3:18" x14ac:dyDescent="0.3">
       <c r="R15" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="3:18" x14ac:dyDescent="0.45">
+    <row r="16" spans="3:18" x14ac:dyDescent="0.3">
       <c r="C16" t="s">
         <v>9</v>
       </c>
@@ -852,7 +880,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C18" t="s">
         <v>10</v>
       </c>
@@ -860,7 +888,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C19" t="s">
         <v>40</v>
       </c>
@@ -868,22 +896,22 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:22" x14ac:dyDescent="0.3">
       <c r="R21" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C22" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:22" x14ac:dyDescent="0.3">
       <c r="R23" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.3">
       <c r="O24" t="s">
         <v>27</v>
       </c>
@@ -894,7 +922,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.45">
+    <row r="25" spans="3:22" x14ac:dyDescent="0.3">
       <c r="O25" t="s">
         <v>28</v>
       </c>
@@ -902,7 +930,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.45">
+    <row r="26" spans="3:22" x14ac:dyDescent="0.3">
       <c r="O26" t="s">
         <v>29</v>
       </c>
@@ -910,22 +938,22 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.45">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.3">
       <c r="R28" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.45">
+    <row r="29" spans="3:22" x14ac:dyDescent="0.3">
       <c r="R29" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:22" x14ac:dyDescent="0.3">
       <c r="R31" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="33" spans="3:33" x14ac:dyDescent="0.45">
+    <row r="33" spans="3:33" x14ac:dyDescent="0.3">
       <c r="R33" t="s">
         <v>32</v>
       </c>
@@ -939,12 +967,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="35" spans="3:33" x14ac:dyDescent="0.45">
+    <row r="35" spans="3:33" x14ac:dyDescent="0.3">
       <c r="R35" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="36" spans="3:33" x14ac:dyDescent="0.45">
+    <row r="36" spans="3:33" x14ac:dyDescent="0.3">
       <c r="C36" t="s">
         <v>42</v>
       </c>
@@ -952,12 +980,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="3:33" x14ac:dyDescent="0.45">
+    <row r="38" spans="3:33" x14ac:dyDescent="0.3">
       <c r="C38" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="40" spans="3:33" x14ac:dyDescent="0.45">
+    <row r="40" spans="3:33" x14ac:dyDescent="0.3">
       <c r="C40" t="s">
         <v>44</v>
       </c>
@@ -965,27 +993,27 @@
         <v>39</v>
       </c>
     </row>
-    <row r="42" spans="3:33" x14ac:dyDescent="0.45">
+    <row r="42" spans="3:33" x14ac:dyDescent="0.3">
       <c r="C42" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="44" spans="3:33" x14ac:dyDescent="0.45">
+    <row r="44" spans="3:33" x14ac:dyDescent="0.3">
       <c r="C44" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="46" spans="3:33" x14ac:dyDescent="0.45">
+    <row r="46" spans="3:33" x14ac:dyDescent="0.3">
       <c r="C46" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="48" spans="3:33" x14ac:dyDescent="0.45">
+    <row r="48" spans="3:33" x14ac:dyDescent="0.3">
       <c r="C48" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C50" t="s">
         <v>49</v>
       </c>
@@ -993,12 +1021,12 @@
         <v>54</v>
       </c>
     </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="51" spans="3:13" x14ac:dyDescent="0.3">
       <c r="M51" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="52" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C52" t="s">
         <v>50</v>
       </c>
@@ -1006,47 +1034,47 @@
         <v>56</v>
       </c>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C53" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="54" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C54" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="56" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C56" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="59" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C59" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C60" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="62" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C62" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C63" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="64" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C64" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="67" spans="3:15" x14ac:dyDescent="0.45">
+    <row r="67" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C67" t="s">
         <v>62</v>
       </c>
@@ -1054,7 +1082,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="68" spans="3:15" x14ac:dyDescent="0.45">
+    <row r="68" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C68" t="s">
         <v>63</v>
       </c>
@@ -1062,7 +1090,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="3:15" x14ac:dyDescent="0.45">
+    <row r="69" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C69" t="s">
         <v>64</v>
       </c>
@@ -1070,22 +1098,22 @@
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="3:15" x14ac:dyDescent="0.45">
+    <row r="70" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C70" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="71" spans="3:15" x14ac:dyDescent="0.45">
+    <row r="71" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C71" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="75" spans="3:15" x14ac:dyDescent="0.45">
+    <row r="75" spans="3:15" x14ac:dyDescent="0.3">
       <c r="O75" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="76" spans="3:15" ht="32" x14ac:dyDescent="0.45">
+    <row r="76" spans="3:15" ht="28.5" x14ac:dyDescent="0.3">
       <c r="C76" t="s">
         <v>69</v>
       </c>
@@ -1093,12 +1121,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="77" spans="3:15" x14ac:dyDescent="0.45">
+    <row r="77" spans="3:15" x14ac:dyDescent="0.3">
       <c r="O77" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="78" spans="3:15" ht="92.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="3:15" ht="92.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C78" t="s">
         <v>70</v>
       </c>
@@ -1106,7 +1134,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="79" spans="3:15" ht="32" x14ac:dyDescent="0.45">
+    <row r="79" spans="3:15" ht="28.5" x14ac:dyDescent="0.3">
       <c r="C79" t="s">
         <v>71</v>
       </c>
@@ -1117,32 +1145,32 @@
         <v>87</v>
       </c>
     </row>
-    <row r="80" spans="3:15" x14ac:dyDescent="0.45">
+    <row r="80" spans="3:15" x14ac:dyDescent="0.3">
       <c r="O80" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.45">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C81" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.45">
+    <row r="83" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C83" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.45">
+    <row r="84" spans="3:15" x14ac:dyDescent="0.3">
       <c r="O84" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.45">
+    <row r="85" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C85" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.45">
+    <row r="86" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C86" t="s">
         <v>75</v>
       </c>
@@ -1150,22 +1178,22 @@
         <v>90</v>
       </c>
     </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.45">
+    <row r="88" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C88" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.45">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C90" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.45">
+    <row r="91" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C91" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.45">
+    <row r="93" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C93" t="s">
         <v>79</v>
       </c>
@@ -1173,12 +1201,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.45">
+    <row r="95" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C95" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="99" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="99" spans="3:17" x14ac:dyDescent="0.3">
       <c r="D99" t="s">
         <v>91</v>
       </c>
@@ -1186,7 +1214,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="100" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="100" spans="3:17" x14ac:dyDescent="0.3">
       <c r="O100" t="s">
         <v>101</v>
       </c>
@@ -1194,7 +1222,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="101" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.3">
       <c r="D101" t="s">
         <v>92</v>
       </c>
@@ -1208,7 +1236,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="102" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.3">
       <c r="D102" t="s">
         <v>93</v>
       </c>
@@ -1222,7 +1250,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="103" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="103" spans="3:17" x14ac:dyDescent="0.3">
       <c r="D103" t="s">
         <v>94</v>
       </c>
@@ -1236,9 +1264,44 @@
         <v>100</v>
       </c>
     </row>
-    <row r="104" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="104" spans="3:17" x14ac:dyDescent="0.3">
       <c r="D104" t="s">
         <v>95</v>
+      </c>
+    </row>
+    <row r="111" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C111" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="114" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C114" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="115" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C115" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="116" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C116" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="117" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C117" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="118" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C118" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="119" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C119" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
